--- a/gex_pivot_levels_2026-10-01.xlsx
+++ b/gex_pivot_levels_2026-10-01.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Pivots" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NQ'!$A$1:$G$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RTY'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CL'!$A$1:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'GC'!$A$1:$G$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,12 +544,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>-$390.23K</t>
+          <t>-$878.01K</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+$404.31K</t>
+          <t>+$909.69K</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -565,24 +565,24 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>7671.7</v>
+        <v>7631.71</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>755</v>
+        <v>7535</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>-$7.04M</t>
+          <t>-$5.76M</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>+$9.29M</t>
+          <t>+$5.80M</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -598,24 +598,24 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7711.83</v>
+        <v>7641.71</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>759</v>
+        <v>7545</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>+$402.00K</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-$1.68M</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+$7.25M</t>
+          <t>+$1.68M</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -631,24 +631,24 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>7721.86</v>
+        <v>7646.71</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>760</v>
+        <v>7550</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>-$13.50M</t>
+          <t>-$9.23M</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>+$21.61M</t>
+          <t>+$9.35M</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -664,10 +664,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7736.71</v>
+        <v>7651.71</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7640</v>
+        <v>7555</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -676,12 +676,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-$6.78M</t>
+          <t>-$1.74M</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>+$9.46M</t>
+          <t>+$1.82M</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -691,82 +691,78 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>7671.7</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>755</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>-$7.04M</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>+$9.29M</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
           <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>7741.71</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>7645</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>+$2.83M</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>+$9.28M</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7741.93</v>
+        <v>7671.71</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>762</v>
+        <v>7575</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>-$4.98M</t>
+          <t>-$5.64M</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>+$9.05M</t>
+          <t>+$6.11M</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>7746.71</v>
+        <v>7696.71</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>7650</v>
+        <v>7600</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -775,12 +771,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>-$9.12M</t>
+          <t>-$10.79M</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>+$25.05M</t>
+          <t>+$11.92M</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -796,10 +792,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7771.71</v>
+        <v>7701.71</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>7675</v>
+        <v>7605</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -808,74 +804,74 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>-$3.18M</t>
+          <t>-$5.85M</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>+$22.00M</t>
+          <t>+$6.16M</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>7706.71</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>7610</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>-$9.79M</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>+$10.89M</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>7772.03</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>765</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>-$22.15M</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>+$59.41M</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="G11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7776.71</v>
+        <v>7711.83</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>7680</v>
+        <v>759</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>-$1.21M</t>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>+$402.00K</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>+$11.50M</t>
+          <t>+$7.25M</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -890,33 +886,33 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>7781.71</v>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>7685</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>-$5.48M</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>+$18.35M</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="A13" s="5" t="n">
+        <v>7721.86</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>760</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>-$13.50M</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>+$21.61M</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -924,24 +920,24 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7782.06</v>
+        <v>7736.71</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>766</v>
+        <v>7640</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>+$9.00M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>-$9.80M</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>+$20.09M</t>
+          <t>+$13.66M</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -951,38 +947,38 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>7796.71</v>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>7700</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="A15" s="2" t="n">
+        <v>7741.71</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>7645</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>+$12.31M</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>+$47.87M</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>+$3.87M</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>+$12.68M</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -990,24 +986,24 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7801.71</v>
+        <v>7741.93</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>7705</v>
+        <v>762</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>+$6.71M</t>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>-$4.98M</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>+$17.63M</t>
+          <t>+$9.05M</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1017,30 +1013,30 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>7806.71</v>
+        <v>7746.71</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>7710</v>
+        <v>7650</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>+$13.17M</t>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>-$11.87M</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>+$21.28M</t>
+          <t>+$32.61M</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -1050,63 +1046,59 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7811.71</v>
+        <v>7756.71</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7715</v>
+        <v>7660</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>+$3.56M</t>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>-$4.34M</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>+$10.35M</t>
+          <t>+$13.14M</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7822.19</v>
+        <v>7771.71</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>770</v>
+        <v>7675</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>+$3.44M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>-$2.97M</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>+$16.95M</t>
+          <t>+$20.52M</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1118,24 +1110,24 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>7826.71</v>
+        <v>7772.03</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>7730</v>
+        <v>765</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>+$9.34M</t>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>-$22.15M</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>+$13.09M</t>
+          <t>+$59.41M</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1145,30 +1137,30 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7841.71</v>
+        <v>7776.71</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>7745</v>
+        <v>7680</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>+$4.70M</t>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>-$1.06M</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>+$6.13M</t>
+          <t>+$10.03M</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1178,30 +1170,30 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>7846.71</v>
+        <v>7781.71</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>7750</v>
+        <v>7685</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>+$10.10M</t>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>-$4.40M</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>+$14.94M</t>
+          <t>+$14.72M</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1211,16 +1203,16 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7862.33</v>
+        <v>7782.06</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
@@ -1229,12 +1221,12 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>+$560.16K</t>
+          <t>+$9.00M</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>+$1.27M</t>
+          <t>+$20.09M</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1244,45 +1236,235 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
+        <v>7796.71</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>7700</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>+$8.02M</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>+$31.17M</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>7801.71</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>7705</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>+$4.10M</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>+$10.79M</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>7806.71</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>7710</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>+$7.61M</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>+$12.31M</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>7822.19</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>+$3.44M</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>+$16.95M</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>7846.71</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>7750</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>+$4.68M</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>+$6.92M</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>7862.33</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>774</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>+$560.16K</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>+$1.27M</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
         <v>7872.36</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B30" s="5" t="n">
         <v>775</v>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>+$5.30M</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>+$6.00M</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G24"/>
+  <autoFilter ref="A1:G30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3920,7 +4102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4016,28 +4198,28 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7796.71</v>
+        <v>30937.95</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>7700</v>
+        <v>740</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>+$12.31M</t>
+          <t>+$9.36M</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>+$47.87M</t>
+          <t>+$46.17M</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -4054,28 +4236,28 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>30937.95</v>
+        <v>7746.71</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>740</v>
+        <v>7650</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>+$9.36M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>-$11.87M</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>+$46.17M</t>
+          <t>+$32.61M</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -4085,7 +4267,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -4096,24 +4278,24 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>7746.71</v>
+        <v>7796.71</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>7650</v>
+        <v>7700</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>-$9.12M</t>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>+$8.02M</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>+$25.05M</t>
+          <t>+$31.17M</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -4123,115 +4305,115 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>7721.86</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>760</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>-$13.50M</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>+$21.61M</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>7771.71</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C7" s="2" t="n">
         <v>7675</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>-$3.18M</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>+$22.00M</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-$2.97M</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>+$20.52M</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>7721.86</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>760</v>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="B8" s="2" t="n">
+        <v>7782.06</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>766</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>-$13.50M</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>+$21.61M</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>7806.71</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>7710</v>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>+$13.17M</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>+$21.28M</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>+$9.00M</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>+$20.09M</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4244,10 +4426,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>7782.06</v>
+        <v>7822.19</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -4256,58 +4438,54 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>+$9.00M</t>
+          <t>+$3.44M</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>+$20.09M</t>
+          <t>+$16.95M</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="5" t="n">
         <v>7781.71</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="5" t="n">
         <v>7685</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-$5.48M</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>+$18.35M</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>-$4.40M</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>+$14.72M</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4320,24 +4498,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>7801.71</v>
+        <v>7736.71</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7705</v>
+        <v>7640</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>+$6.71M</t>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-$9.80M</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>+$17.63M</t>
+          <t>+$13.66M</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -4352,148 +4530,148 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>31143.48</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>745</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>+$7.56M</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>+$13.29M</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>7822.19</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>+$3.44M</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>+$16.95M</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="B13" s="2" t="n">
+        <v>7756.71</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>7660</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-$4.34M</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>+$13.14M</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>7846.71</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>7750</v>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="B14" s="2" t="n">
+        <v>7741.71</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>7645</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>+$10.10M</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>+$14.94M</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>31143.48</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>745</v>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>+$7.56M</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>+$13.29M</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>+$3.87M</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>+$12.68M</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>7826.71</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>7730</v>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="B15" s="2" t="n">
+        <v>7806.71</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>7710</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>+$9.34M</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>+$13.09M</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>+$7.61M</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>+$12.31M</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4538,106 +4716,102 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>7776.71</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>7680</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="B17" s="5" t="n">
+        <v>7696.71</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>7600</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>-$1.21M</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>+$11.50M</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>-$10.79M</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>+$11.92M</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>4310.77</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>-$6.90M</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>+$10.57M</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>7706.71</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>7610</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-$9.79M</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>+$10.89M</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>30855.74</v>
+        <v>7801.71</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>738</v>
+        <v>7705</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>+$4.66M</t>
+          <t>+$4.10M</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>+$10.39M</t>
+          <t>+$10.79M</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -4647,43 +4821,43 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>7811.71</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>7715</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>+$3.56M</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>+$10.35M</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>4310.77</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>-$6.90M</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>+$10.57M</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4692,188 +4866,188 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>30855.74</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>738</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>+$4.66M</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>+$10.39M</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>7736.71</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>7640</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="B22" s="2" t="n">
+        <v>7776.71</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>7680</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>-$6.78M</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>+$9.46M</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>-$1.06M</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>+$10.03M</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>7646.71</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>7550</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>-$9.23M</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>+$9.35M</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B24" s="5" t="n">
         <v>7671.7</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C24" s="5" t="n">
         <v>755</v>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>-$7.04M</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>+$9.29M</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
-        <v>7741.71</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>7645</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>+$2.83M</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>+$9.28M</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
+      <c r="B25" s="2" t="n">
         <v>7741.93</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C25" s="2" t="n">
         <v>762</v>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>-$4.98M</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>+$9.05M</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>2816.8</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>280</v>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>+$997.79K</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>+$8.98M</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4882,74 +5056,74 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>2816.8</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>+$997.79K</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>+$8.98M</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B27" s="5" t="n">
         <v>31349.01</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C27" s="5" t="n">
         <v>750</v>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>+$5.24M</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>+$8.49M</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>31225.69</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>747</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>+$6.30M</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>+$7.79M</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4962,362 +5136,354 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>30526.9</v>
+        <v>31225.69</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>730</v>
+        <v>747</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>-$1.49M</t>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>+$6.30M</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>+$7.60M</t>
+          <t>+$7.79M</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2796.68</v>
+        <v>30526.9</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>278</v>
+        <v>730</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>-$4.23M</t>
+          <t>-$1.49M</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>+$7.35M</t>
+          <t>+$7.60M</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>2796.68</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>-$4.23M</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>+$7.35M</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B31" s="2" t="n">
         <v>7711.83</v>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C31" s="2" t="n">
         <v>759</v>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>+$402.00K</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>+$7.25M</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B32" s="5" t="n">
         <v>4502.36</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>+$6.42M</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>+$7.21M</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
-        <v>7841.71</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>7745</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="B33" s="2" t="n">
+        <v>7846.71</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>7750</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>+$4.70M</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>+$6.13M</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>+$4.68M</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>+$6.92M</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>7872.36</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>775</v>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>+$5.30M</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>+$6.00M</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>4119.18</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>-$5.11M</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>+$5.17M</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="B34" s="2" t="n">
+        <v>7701.71</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>7605</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>-$5.85M</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>+$6.16M</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>30979.06</v>
+        <v>7671.71</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>741</v>
+        <v>7575</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>-$296.60K</t>
+          <t>-$5.64M</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>+$4.88M</t>
+          <t>+$6.11M</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>31184.59</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>746</v>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>+$3.32M</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>+$4.80M</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>7872.36</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>775</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>+$5.30M</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>+$6.00M</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>88.73999999999999</v>
+        <v>7631.71</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>145</v>
+        <v>7535</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>-$2.39M</t>
+          <t>-$5.76M</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>+$4.63M</t>
+          <t>+$5.80M</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -5334,28 +5500,28 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>2857.04</v>
+        <v>4119.18</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>284</v>
+        <v>86</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>+$3.84M</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>-$5.11M</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>+$4.48M</t>
+          <t>+$5.17M</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -5365,35 +5531,35 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>2826.86</v>
+        <v>30979.06</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>281</v>
+        <v>741</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>-$1.10M</t>
+          <t>-$296.60K</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>+$4.35M</t>
+          <t>+$4.88M</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -5408,38 +5574,38 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>-$4.00M</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>+$4.10M</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>31184.59</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>746</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>+$3.32M</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>+$4.80M</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -5448,28 +5614,28 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>4214.98</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>USO</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>-$3.56M</t>
+          <t>-$2.39M</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>+$3.89M</t>
+          <t>+$4.63M</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -5486,188 +5652,188 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>2857.04</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>284</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>+$3.84M</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>+$4.48M</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>2826.86</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>-$1.10M</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>+$4.35M</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B44" s="5" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>-$4.00M</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>+$4.10M</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>4214.98</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>-$3.56M</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>+$3.89M</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
         <v>89.95999999999999</v>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C46" s="5" t="n">
         <v>147</v>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>-$2.99M</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>+$3.87M</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>+$1.54M</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>+$3.80M</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>4334.72</v>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>+$3.47M</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>+$3.76M</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>30362.48</v>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>726</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>-$3.23M</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>+$3.33M</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>31307.9</v>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>749</v>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>+$2.59M</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>+$3.05M</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -5680,24 +5846,24 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>85.68000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>-$2.13M</t>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>+$1.54M</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>+$2.99M</t>
+          <t>+$3.80M</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -5707,35 +5873,35 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>31636.74</v>
+        <v>4334.72</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>757</v>
+        <v>90.5</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>+$2.87M</t>
+          <t>+$3.47M</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>+$2.87M</t>
+          <t>+$3.76M</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -5752,70 +5918,78 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>4071.29</v>
+        <v>30362.48</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>85</v>
+        <v>726</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>-$1.90M</t>
+          <t>-$3.23M</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>+$2.69M</t>
+          <t>+$3.33M</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>4262.88</v>
+        <v>31307.9</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>89</v>
+        <v>749</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>-$1.39M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>+$2.59M</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>+$2.47M</t>
+          <t>+$3.05M</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -5824,10 +5998,10 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>82.62</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
@@ -5836,12 +6010,12 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>-$2.29M</t>
+          <t>-$2.13M</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>+$2.47M</t>
+          <t>+$2.99M</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -5856,40 +6030,40 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>4251.34</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>385</v>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>-$320</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>+$2.41M</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>31636.74</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>757</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>+$2.87M</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>+$2.87M</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -5900,24 +6074,24 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>4196.12</v>
+        <v>4071.29</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>380</v>
+        <v>85</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>-$414.70K</t>
+          <t>-$1.90M</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>+$2.34M</t>
+          <t>+$2.69M</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -5934,10 +6108,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>4167.08</v>
+        <v>4262.88</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -5946,12 +6120,12 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>-$2.02M</t>
+          <t>-$1.39M</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>+$2.21M</t>
+          <t>+$2.47M</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -5962,38 +6136,42 @@
       <c r="H54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>4646.06</v>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>+$1.39M</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>+$2.13M</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr"/>
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>82.62</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>-$2.29M</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>+$2.47M</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -6002,24 +6180,24 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>4174.04</v>
+        <v>4251.34</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>+$135.11K</t>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>-$320</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>+$2.06M</t>
+          <t>+$2.41M</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
@@ -6029,73 +6207,69 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
-        <v>4229.25</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>383</v>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="B57" s="2" t="n">
+        <v>4196.12</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>+$1.52M</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>+$2.04M</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>-$414.70K</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>+$2.34M</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>94.23999999999999</v>
+        <v>4167.08</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>+$1.24M</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>-$2.02M</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>+$1.80M</t>
+          <t>+$2.21M</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -6108,40 +6282,36 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>93.63</v>
+        <v>4646.06</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>+$1.34M</t>
+          <t>+$1.39M</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>+$1.56M</t>
+          <t>+$2.13M</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -6150,24 +6320,24 @@
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>4140.91</v>
+        <v>4174.04</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>-$1.35M</t>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>+$135.11K</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>+$1.42M</t>
+          <t>+$2.06M</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -6177,155 +6347,155 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>7862.33</v>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>774</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>+$560.16K</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>+$1.27M</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>4229.25</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>383</v>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>+$1.52M</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>+$2.04M</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>4023.39</v>
+        <v>7651.71</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>84</v>
+        <v>7555</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>-$1.24M</t>
+          <t>-$1.74M</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>+$1.26M</t>
+          <t>+$1.82M</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>+$1.24M</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>+$1.80M</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>4430.52</v>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>-$335.73K</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>+$1.25M</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="H63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="n">
-        <v>79.56</v>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>-$1.03M</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>+$1.06M</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>7641.71</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>7545</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>-$1.68M</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>+$1.68M</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -6336,24 +6506,24 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>88.12</v>
+        <v>93.63</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>-$450.67K</t>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>+$1.34M</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>+$933.70K</t>
+          <t>+$1.56M</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -6368,64 +6538,68 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>93.02</v>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>+$283.14K</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>+$873.37K</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr"/>
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>4140.91</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>-$1.35M</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>+$1.42M</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>4163</v>
+        <v>7862.33</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>377</v>
+        <v>774</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>-$735.61K</t>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>+$560.16K</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>+$863.14K</t>
+          <t>+$1.27M</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -6446,10 +6620,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>4143.13</v>
+        <v>4023.39</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>86.5</v>
+        <v>84</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -6458,130 +6632,130 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>-$602.48K</t>
+          <t>-$1.24M</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>+$821.38K</t>
+          <t>+$1.26M</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>4430.52</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>-$335.73K</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>+$1.25M</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n">
-        <v>97.92</v>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="B70" s="5" t="n">
+        <v>79.56</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>+$732.02K</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>+$814.79K</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-$1.03M</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>+$1.06M</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n">
-        <v>86.29000000000001</v>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="B71" s="2" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>-$601.52K</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>+$805.63K</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="n">
-        <v>4284.46</v>
-      </c>
-      <c r="C71" s="5" t="n">
-        <v>388</v>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>+$596.81K</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>+$794.42K</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>-$450.67K</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>+$933.70K</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -6590,28 +6764,28 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>4286.83</v>
+        <v>7626.71</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>89.5</v>
+        <v>7530</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>+$569.80K</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>-$878.01K</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>+$739.90K</t>
+          <t>+$909.69K</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -6632,36 +6806,32 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>89.34999999999999</v>
+        <v>93.02</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>-$424.26K</t>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>+$283.14K</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>+$718.28K</t>
+          <t>+$873.37K</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -6670,10 +6840,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>4185.08</v>
+        <v>4163</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -6682,12 +6852,12 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>-$579.03K</t>
+          <t>-$735.61K</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>+$681.40K</t>
+          <t>+$863.14K</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -6702,80 +6872,76 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="n">
-        <v>31020</v>
-      </c>
-      <c r="C75" s="5" t="n">
-        <v>30500</v>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>+$262.73K</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>+$583.84K</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>4143.13</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>-$602.48K</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>+$821.38K</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="n">
-        <v>4361.76</v>
-      </c>
-      <c r="C76" s="5" t="n">
-        <v>395</v>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>+$563.77K</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>+$574.73K</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>97.92</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>+$732.02K</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>+$814.79K</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -6784,10 +6950,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>80.78</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
@@ -6796,84 +6962,88 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>-$526.73K</t>
+          <t>-$601.52K</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>+$534.67K</t>
+          <t>+$805.63K</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="n">
-        <v>92.41</v>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>-$8.61K</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>+$525.84K</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>4284.46</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>388</v>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>+$596.81K</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>+$794.42K</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>31513.43</v>
+        <v>4286.83</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>754</v>
+        <v>89.5</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>+$488.12K</t>
+          <t>+$569.80K</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>+$507.11K</t>
+          <t>+$739.90K</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -6883,35 +7053,35 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>4295.51</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>389</v>
+        <v>146</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>USO</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>-$200.88K</t>
+          <t>-$424.26K</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>+$474.56K</t>
+          <t>+$718.28K</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -6921,35 +7091,35 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>7626.71</v>
+        <v>4185.08</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>7530</v>
+        <v>379</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>-$390.23K</t>
+          <t>-$579.03K</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>+$404.31K</t>
+          <t>+$681.40K</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -6959,7 +7129,7 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -6970,10 +7140,10 @@
         </is>
       </c>
       <c r="B82" s="5" t="n">
-        <v>30860</v>
+        <v>31020</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>30340</v>
+        <v>30500</v>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
@@ -6982,12 +7152,12 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>+$364.90K</t>
+          <t>+$262.73K</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>+$379.50K</t>
+          <t>+$583.84K</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -7002,80 +7172,76 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n">
-        <v>4151.95</v>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>376</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="B83" s="5" t="n">
+        <v>4361.76</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>395</v>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>-$248.61K</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>+$266.89K</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>+$563.77K</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>+$574.73K</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="n">
-        <v>30920</v>
-      </c>
-      <c r="C84" s="5" t="n">
-        <v>30400</v>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>-$102.17K</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>+$248.13K</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>-$526.73K</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>+$534.67K</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -7084,10 +7250,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>83.23</v>
+        <v>92.41</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
@@ -7096,12 +7262,12 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>-$144.93K</t>
+          <t>-$8.61K</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>+$192.47K</t>
+          <t>+$525.84K</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -7111,77 +7277,85 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>4085.7</v>
+        <v>31513.43</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>370</v>
+        <v>754</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>-$183.78K</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>+$488.12K</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>+$188.20K</t>
+          <t>+$507.11K</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>30960</v>
+        <v>4295.51</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>30440</v>
+        <v>389</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>-$36.49K</t>
+          <t>-$200.88K</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>+$182.45K</t>
+          <t>+$474.56K</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -7190,24 +7364,24 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>30820</v>
+        <v>30860</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>30300</v>
+        <v>30340</v>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>-$80.28K</t>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>+$364.90K</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>+$173.94K</t>
+          <t>+$379.50K</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -7217,111 +7391,119 @@
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>4151.95</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>-$248.61K</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>+$266.89K</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n">
-        <v>31120</v>
-      </c>
-      <c r="C89" s="2" t="n">
-        <v>30600</v>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="B90" s="5" t="n">
+        <v>30920</v>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>30400</v>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>+$66.90K</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>+$173.94K</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="n">
-        <v>30790</v>
-      </c>
-      <c r="C90" s="2" t="n">
-        <v>30270</v>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>-$43.48K</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>+$163.90K</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr"/>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>-$102.17K</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>+$248.13K</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="n">
-        <v>30895</v>
-      </c>
-      <c r="C91" s="5" t="n">
-        <v>30375</v>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>+$91.23K</t>
-        </is>
-      </c>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>+$113.12K</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H91" s="6" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>83.23</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>-$144.93K</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>+$192.47K</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -7330,108 +7512,104 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>4085.7</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>-$183.78K</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>+$188.20K</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n">
-        <v>31070</v>
-      </c>
-      <c r="C92" s="2" t="n">
-        <v>30550</v>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="B93" s="2" t="n">
+        <v>30960</v>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>30440</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>+$23.41K</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>+$103.69K</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>-$36.49K</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>+$182.45K</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="H93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B93" s="5" t="n">
-        <v>30770</v>
-      </c>
-      <c r="C93" s="5" t="n">
-        <v>30250</v>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="B94" s="5" t="n">
+        <v>30820</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>30300</v>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>-$85.14K</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>+$103.39K</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>-$80.28K</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>+$173.94K</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H93" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="n">
-        <v>30870</v>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v>30350</v>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>-$21.89K</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t>+$80.28K</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H94" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -7444,10 +7622,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>30980</v>
+        <v>31120</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>30460</v>
+        <v>30600</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
@@ -7456,98 +7634,90 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>+$65.68K</t>
+          <t>+$66.90K</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>+$80.28K</t>
+          <t>+$173.94K</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>80.17</v>
+        <v>30790</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>131</v>
+        <v>30270</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>-$63.62K</t>
+          <t>-$43.48K</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>+$75.51K</t>
+          <t>+$163.90K</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n">
-        <v>30995</v>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v>30475</v>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="B97" s="5" t="n">
+        <v>30895</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>30375</v>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>-$25.54K</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>+$69.33K</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>+$91.23K</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>+$113.12K</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -7558,39 +7728,263 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
+        <v>31070</v>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>30550</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>+$23.41K</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>+$103.69K</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>30770</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>30250</v>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>-$85.14K</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>+$103.39K</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>30870</v>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>30350</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>-$21.89K</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>+$80.28K</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>30980</v>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>30460</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>+$65.68K</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>+$80.28K</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>80.17</v>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>-$63.62K</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>+$75.51K</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>30995</v>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>30475</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>-$25.54K</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>+$69.33K</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
         <v>30795</v>
       </c>
-      <c r="C98" s="2" t="n">
+      <c r="C104" s="2" t="n">
         <v>30275</v>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr">
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>+$26.76K</t>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H98"/>
+  <autoFilter ref="A1:H104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>